--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$30</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="284">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -519,495 +519,64 @@
     <t>Philippines Department of Health National Health Facilities Registry Code</t>
   </si>
   <si>
-    <t>Organization.identifier:NhfrCode.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t>Organization.identifier:PAN</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>PhilHealth Accreditation Number</t>
+  </si>
+  <si>
+    <t>Organization.identifier:PEN</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t>PhilHealth Employer Number</t>
+  </si>
+  <si>
+    <t>Organization.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>official</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
+    <t>Whether the organization's record is still in active use</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use.</t>
+  </si>
+  <si>
+    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>No equivalent in HL7 v2</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Organization.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.text</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://doh.gov.ph/fhir/Identifier/doh-nhfr-code</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.active</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
-  </si>
-  <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
-This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>No equivalent in HL7 v2</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Organization.type</t>
   </si>
   <si>
     <t>Kind of organization</t>
@@ -1039,10 +608,17 @@
     <t>.code</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>FiveWs.class</t>
   </si>
   <si>
     <t>Organization.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Name used for the organization</t>
@@ -1121,7 +697,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -1157,6 +733,10 @@
     <t>Organization.partOf</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
+</t>
+  </si>
+  <si>
     <t>The organization of which this organization forms a part</t>
   </si>
   <si>
@@ -1194,7 +774,22 @@
     <t>Organization.contact.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>Organization.contact.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Organization.contact.modifierExtension</t>
@@ -1224,6 +819,9 @@
   </si>
   <si>
     <t>Need to distinguish between multiple contact persons.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>The purpose for which you would contact a contact party.</t>
@@ -1623,11 +1221,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.95703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.03125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.09765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.09765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1636,7 +1234,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1645,24 +1243,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="46.38671875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="41.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="27.49609375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.6953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3043,14 +2641,16 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3059,28 +2659,30 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3128,43 +2730,45 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3174,27 +2778,27 @@
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3230,19 +2834,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3251,30 +2855,30 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3288,7 +2892,7 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>88</v>
@@ -3297,29 +2901,31 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="R15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>77</v>
@@ -3334,13 +2940,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3358,7 +2964,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3373,24 +2979,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3401,7 +3007,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3413,19 +3019,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3450,13 +3056,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3474,13 +3080,13 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
@@ -3489,24 +3095,24 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3520,25 +3126,29 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3586,7 +3196,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3595,19 +3205,19 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3618,11 +3228,11 @@
         <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3641,18 +3251,20 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3688,19 +3300,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3712,13 +3324,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3727,12 +3339,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3746,28 +3358,28 @@
         <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3816,7 +3428,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3825,30 +3437,30 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3859,10 +3471,10 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -3871,16 +3483,20 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3928,28 +3544,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3957,21 +3573,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3980,21 +3596,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4030,40 +3646,40 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4071,10 +3687,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4085,7 +3701,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4094,29 +3710,29 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -4158,13 +3774,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4173,10 +3789,10 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4187,10 +3803,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4210,20 +3826,18 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4272,7 +3886,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4284,13 +3898,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4301,21 +3915,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4324,27 +3938,27 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>77</v>
@@ -4386,25 +4000,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4415,43 +4029,45 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>142</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4500,25 +4116,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4529,7 +4145,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>252</v>
@@ -4552,22 +4168,20 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4592,13 +4206,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4616,7 +4230,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4631,10 +4245,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4645,10 +4259,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4668,22 +4282,20 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4732,7 +4344,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4747,10 +4359,10 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4761,10 +4373,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4772,10 +4384,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4784,35 +4396,33 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4848,13 +4458,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -4863,24 +4473,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4894,27 +4504,27 @@
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4926,7 +4536,7 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -4962,7 +4572,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4977,13 +4587,13 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4991,10 +4601,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5005,7 +4615,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5014,19 +4624,21 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5074,13 +4686,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5089,1974 +4701,20 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>299</v>
+        <v>189</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q32" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="R32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="P37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" hidden="true">
-      <c r="A38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="P38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN47">
+  <autoFilter ref="A1:AN30">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7066,7 +4724,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="283">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,10 +513,8 @@
     <t>NhfrCode</t>
   </si>
   <si>
-    <t>DOH NHFR Code</t>
-  </si>
-  <si>
-    <t>Philippines Department of Health National Health Facilities Registry Code</t>
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-doh-nhfr-code}
+</t>
   </si>
   <si>
     <t>Organization.identifier:PAN</t>
@@ -525,7 +523,8 @@
     <t>PAN</t>
   </si>
   <si>
-    <t>PhilHealth Accreditation Number</t>
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-philhealth-pan}
+</t>
   </si>
   <si>
     <t>Organization.identifier:PEN</t>
@@ -534,7 +533,8 @@
     <t>PEN</t>
   </si>
   <si>
-    <t>PhilHealth Employer Number</t>
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-philhealth-pen}
+</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1234,7 +1234,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.87109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.7734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2555,13 +2555,13 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -2643,13 +2643,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2671,10 +2671,10 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>147</v>
@@ -2759,13 +2759,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
@@ -2787,10 +2787,10 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>147</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2901,26 +2901,26 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="O15" t="s" s="2">
+      <c r="P15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="P15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q15" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="R15" t="s" s="2">
         <v>77</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2979,24 +2979,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>177</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3019,19 +3019,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3056,14 +3056,14 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3095,24 +3095,24 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3135,19 +3135,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3196,7 +3196,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3211,13 +3211,13 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3251,19 +3251,19 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3312,7 +3312,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3330,7 +3330,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3367,19 +3367,19 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3428,7 +3428,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3437,19 +3437,19 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="AK19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3457,10 +3457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3483,19 +3483,19 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3544,7 +3544,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3553,19 +3553,19 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AJ20" t="s" s="2">
+      <c r="AK20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AK20" t="s" s="2">
+      <c r="AL20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3599,17 +3599,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3658,7 +3658,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3673,13 +3673,13 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3713,19 +3713,19 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3774,7 +3774,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3792,7 +3792,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3829,13 +3829,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3886,7 +3886,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3904,7 +3904,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3947,7 +3947,7 @@
         <v>134</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>136</v>
@@ -4000,7 +4000,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4018,7 +4018,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4029,14 +4029,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4058,10 +4058,10 @@
         <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>136</v>
@@ -4116,7 +4116,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4171,17 +4171,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4206,14 +4206,14 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>258</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4248,7 +4248,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4285,17 +4285,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4344,7 +4344,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4359,10 +4359,10 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4399,17 +4399,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4458,7 +4458,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4473,10 +4473,10 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4513,17 +4513,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4572,7 +4572,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4587,10 +4587,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4601,10 +4601,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4627,17 +4627,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4686,7 +4686,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4704,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -614,13 +614,210 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Organization.name</t>
+    <t>Organization.type.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Organization.type.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Organization.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Organization.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Organization.name</t>
+  </si>
+  <si>
     <t>Name used for the organization</t>
   </si>
   <si>
@@ -774,22 +971,7 @@
     <t>Organization.contact.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Organization.contact.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Organization.contact.modifierExtension</t>
@@ -831,6 +1013,39 @@
   </si>
   <si>
     <t>./type</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.code</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.display</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.text</t>
   </si>
   <si>
     <t>Organization.contact.name</t>
@@ -1221,11 +1436,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.09765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.09765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1252,14 +1467,14 @@
     <col min="26" max="26" width="41.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="27.49609375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.6953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -2991,7 +3206,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>177</v>
       </c>
@@ -3010,7 +3225,7 @@
         <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -3107,7 +3322,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>190</v>
       </c>
@@ -3126,13 +3341,13 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>191</v>
@@ -3143,12 +3358,8 @@
       <c r="M17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3196,7 +3407,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3205,19 +3416,19 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3225,14 +3436,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3251,20 +3462,18 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3300,16 +3509,16 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>199</v>
@@ -3324,13 +3533,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3341,10 +3550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3364,22 +3573,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3428,7 +3637,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3437,30 +3646,30 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3471,10 +3680,10 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -3483,20 +3692,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3544,28 +3749,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3573,21 +3778,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3596,21 +3801,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3646,40 +3851,40 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3687,10 +3892,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3701,7 +3906,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3710,22 +3915,22 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3774,13 +3979,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -3789,10 +3994,10 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3803,10 +4008,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3826,18 +4031,20 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3886,7 +4093,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3898,13 +4105,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3913,46 +4120,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4000,25 +4207,25 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4029,45 +4236,43 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4116,25 +4321,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4145,10 +4350,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4168,20 +4373,22 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4206,13 +4413,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4230,7 +4437,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4245,10 +4452,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4259,10 +4466,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4282,20 +4489,22 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4344,7 +4553,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4359,10 +4568,10 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4371,12 +4580,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4387,29 +4596,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4458,39 +4669,39 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4501,10 +4712,10 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
@@ -4513,17 +4724,19 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4572,13 +4785,13 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -4587,10 +4800,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4599,12 +4812,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4618,7 +4831,7 @@
         <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -4627,17 +4840,19 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4686,7 +4901,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4695,26 +4910,2542 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="AJ30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AK32" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN30">
+  <autoFilter ref="A1:AN52">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4724,7 +7455,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI29">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="308">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -674,123 +674,6 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Organization.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Organization.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Organization.type.text</t>
   </si>
   <si>
@@ -1022,27 +905,6 @@
   </si>
   <si>
     <t>Organization.contact.purpose.coding</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.contact.purpose.coding.userSelected</t>
   </si>
   <si>
     <t>Organization.contact.purpose.text</t>
@@ -1436,11 +1298,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.42578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3664,7 +3526,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>209</v>
       </c>
@@ -3683,25 +3545,29 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3749,7 +3615,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3761,13 +3627,13 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3776,46 +3642,48 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3851,40 +3719,40 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3892,10 +3760,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3906,7 +3774,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3915,22 +3783,22 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3979,13 +3847,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -3994,10 +3862,10 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4006,12 +3874,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4022,30 +3890,32 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4093,28 +3963,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>237</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4122,10 +3992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4136,7 +4006,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>88</v>
@@ -4145,20 +4015,22 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4207,28 +4079,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>248</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4236,10 +4108,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4262,17 +4134,17 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4321,7 +4193,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4336,13 +4208,13 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4350,10 +4222,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4364,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4373,22 +4245,22 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4437,13 +4309,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4452,10 +4324,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4466,10 +4338,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4489,23 +4361,19 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4553,7 +4421,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4565,13 +4433,13 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4580,48 +4448,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4669,28 +4535,28 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>262</v>
+        <v>188</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4698,14 +4564,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4718,25 +4584,25 @@
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4785,7 +4651,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4797,13 +4663,13 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4814,10 +4680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4828,7 +4694,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>88</v>
@@ -4840,19 +4706,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4877,13 +4741,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4901,34 +4765,34 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>276</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>280</v>
       </c>
@@ -4944,10 +4808,10 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -4956,20 +4820,16 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5017,28 +4877,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>188</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5046,21 +4906,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5069,21 +4929,21 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>292</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5119,51 +4979,51 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>199</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>296</v>
+        <v>188</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5177,28 +5037,28 @@
         <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>298</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>302</v>
+        <v>205</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5247,7 +5107,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>206</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5262,10 +5122,10 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>303</v>
+        <v>208</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5274,12 +5134,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5293,25 +5153,29 @@
         <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5359,7 +5223,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5371,13 +5235,13 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5388,21 +5252,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5414,18 +5278,18 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5473,25 +5337,25 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5502,14 +5366,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5522,25 +5386,23 @@
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>231</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>142</v>
+        <v>294</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5589,7 +5451,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5601,13 +5463,13 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>130</v>
+        <v>296</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5618,10 +5480,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5644,17 +5506,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5679,13 +5541,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5703,7 +5565,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5718,10 +5580,10 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5732,10 +5594,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5746,7 +5608,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5758,16 +5620,18 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>304</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>193</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5815,19 +5679,19 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>194</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -5842,1610 +5706,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="P48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN52">
+  <autoFilter ref="A1:AN38">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7455,7 +5717,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
